--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17095,7 +17095,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17557,7 +17557,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21323,7 +21323,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21785,7 +21785,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22324,7 +22324,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22786,7 +22786,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23793,7 +23793,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23872,7 +23872,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25215,7 +25215,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25294,7 +25294,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26400,7 +26400,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26554,7 +26554,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26708,7 +26708,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26862,7 +26862,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27016,7 +27016,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27247,7 +27247,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27555,7 +27555,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27940,7 +27940,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28017,7 +28017,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28171,7 +28171,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28248,7 +28248,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28325,7 +28325,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28633,7 +28633,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29342,7 +29342,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29500,7 +29500,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30211,7 +30211,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30448,7 +30448,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30922,7 +30922,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31159,7 +31159,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31317,7 +31317,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31396,7 +31396,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31475,7 +31475,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31785,7 +31785,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31939,7 +31939,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33325,7 +33325,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33633,7 +33633,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33787,7 +33787,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34338,7 +34338,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34812,7 +34812,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34891,7 +34891,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35128,7 +35128,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35286,7 +35286,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35444,7 +35444,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35602,7 +35602,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35681,7 +35681,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35839,7 +35839,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35918,7 +35918,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35997,7 +35997,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36076,7 +36076,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36234,7 +36234,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36392,7 +36392,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36629,7 +36629,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36785,7 +36785,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -36939,7 +36939,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37016,7 +37016,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37093,7 +37093,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37170,7 +37170,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37247,7 +37247,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37401,7 +37401,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37478,7 +37478,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37632,7 +37632,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37709,7 +37709,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37786,7 +37786,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37863,7 +37863,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38017,7 +38017,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38479,7 +38479,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38556,7 +38556,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38710,7 +38710,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38787,7 +38787,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -38941,7 +38941,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39018,7 +39018,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39095,7 +39095,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39253,7 +39253,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39332,7 +39332,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39490,7 +39490,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39727,7 +39727,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -39885,7 +39885,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -39964,7 +39964,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40043,7 +40043,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40359,7 +40359,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40438,7 +40438,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40833,7 +40833,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -40912,7 +40912,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -40991,7 +40991,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41070,7 +41070,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41228,7 +41228,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41307,7 +41307,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41465,7 +41465,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41544,7 +41544,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41623,7 +41623,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41702,7 +41702,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41781,7 +41781,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -41860,7 +41860,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -41937,7 +41937,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42014,7 +42014,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42091,7 +42091,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42168,7 +42168,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42245,7 +42245,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42476,7 +42476,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42553,7 +42553,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -42861,7 +42861,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -42938,7 +42938,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43015,7 +43015,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43169,7 +43169,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43246,7 +43246,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43477,7 +43477,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43631,7 +43631,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43708,7 +43708,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -43862,7 +43862,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -43939,7 +43939,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44170,7 +44170,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44405,7 +44405,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44563,7 +44563,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -44879,7 +44879,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -44958,7 +44958,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45037,7 +45037,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45274,7 +45274,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45432,7 +45432,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45511,7 +45511,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45590,7 +45590,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -45827,7 +45827,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -45906,7 +45906,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -45985,7 +45985,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46064,7 +46064,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46380,7 +46380,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46459,7 +46459,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46538,7 +46538,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46617,7 +46617,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -46854,7 +46854,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -46933,7 +46933,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47089,7 +47089,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47166,7 +47166,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47320,7 +47320,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47474,7 +47474,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47551,7 +47551,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -47628,7 +47628,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -47705,7 +47705,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -47782,7 +47782,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -47859,7 +47859,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -47936,7 +47936,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48013,7 +48013,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48090,7 +48090,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48167,7 +48167,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48321,7 +48321,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48398,7 +48398,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48475,7 +48475,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -48629,7 +48629,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -48706,7 +48706,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -48783,7 +48783,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -48860,7 +48860,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -48937,7 +48937,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49014,7 +49014,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49091,7 +49091,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49168,7 +49168,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49322,7 +49322,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49399,7 +49399,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49478,7 +49478,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -49557,7 +49557,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -49636,7 +49636,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -49715,7 +49715,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -49794,7 +49794,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -49873,7 +49873,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -49952,7 +49952,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50031,7 +50031,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50110,7 +50110,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50189,7 +50189,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50268,7 +50268,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50347,7 +50347,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50426,7 +50426,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50505,7 +50505,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -50663,7 +50663,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -50742,7 +50742,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -50821,7 +50821,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -50900,7 +50900,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -50979,7 +50979,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51058,7 +51058,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51137,7 +51137,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51216,7 +51216,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51295,7 +51295,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -51532,7 +51532,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -51690,7 +51690,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -51769,7 +51769,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -51848,7 +51848,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -51927,7 +51927,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52006,7 +52006,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52085,7 +52085,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52164,7 +52164,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52249,7 +52249,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q666"/>
+  <dimension ref="A1:Q667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17095,7 +17095,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17557,7 +17557,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21323,7 +21323,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21785,7 +21785,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22324,7 +22324,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22786,7 +22786,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23793,7 +23793,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23872,7 +23872,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25215,7 +25215,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25294,7 +25294,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26400,7 +26400,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26554,7 +26554,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26708,7 +26708,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26862,7 +26862,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27016,7 +27016,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27247,7 +27247,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27555,7 +27555,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27940,7 +27940,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28017,7 +28017,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28171,7 +28171,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28248,7 +28248,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28325,7 +28325,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28633,7 +28633,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29342,7 +29342,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29500,7 +29500,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30211,7 +30211,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30448,7 +30448,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30922,7 +30922,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31159,7 +31159,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31317,7 +31317,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31396,7 +31396,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31475,7 +31475,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31785,7 +31785,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31939,7 +31939,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33325,7 +33325,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33633,7 +33633,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33787,7 +33787,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34338,7 +34338,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34812,7 +34812,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34891,7 +34891,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35128,7 +35128,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35286,7 +35286,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35444,7 +35444,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35602,7 +35602,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35681,7 +35681,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35839,7 +35839,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35918,7 +35918,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35997,7 +35997,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36076,7 +36076,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36234,7 +36234,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36392,7 +36392,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36629,7 +36629,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36785,7 +36785,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -36939,7 +36939,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37016,7 +37016,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37093,7 +37093,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37170,7 +37170,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37247,7 +37247,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37401,7 +37401,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37478,7 +37478,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37632,7 +37632,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37709,7 +37709,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37786,7 +37786,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37863,7 +37863,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38017,7 +38017,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38479,7 +38479,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38556,7 +38556,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38710,7 +38710,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38787,7 +38787,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -38941,7 +38941,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39018,7 +39018,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39095,7 +39095,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39253,7 +39253,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39332,7 +39332,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39490,7 +39490,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39727,7 +39727,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -39885,7 +39885,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -39964,7 +39964,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40043,7 +40043,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40359,7 +40359,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40438,7 +40438,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40833,7 +40833,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -40912,7 +40912,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -40991,7 +40991,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41070,7 +41070,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41228,7 +41228,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41307,7 +41307,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41465,7 +41465,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41544,7 +41544,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41623,7 +41623,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41702,7 +41702,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41781,7 +41781,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -41860,7 +41860,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -41937,7 +41937,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42014,7 +42014,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42091,7 +42091,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42168,7 +42168,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42245,7 +42245,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42476,7 +42476,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42553,7 +42553,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -42861,7 +42861,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -42938,7 +42938,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43015,7 +43015,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43169,7 +43169,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43246,7 +43246,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43477,7 +43477,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43631,7 +43631,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43708,7 +43708,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -43862,7 +43862,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -43939,7 +43939,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44170,7 +44170,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44405,7 +44405,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44563,7 +44563,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -44879,7 +44879,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -44958,7 +44958,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45037,7 +45037,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45274,7 +45274,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45432,7 +45432,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45511,7 +45511,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45590,7 +45590,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -45827,7 +45827,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -45906,7 +45906,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -45985,7 +45985,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46064,7 +46064,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46380,7 +46380,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46459,7 +46459,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46538,7 +46538,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46617,7 +46617,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -46854,7 +46854,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -46933,7 +46933,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47089,10 +47089,14 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q601" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q601" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
@@ -47166,10 +47170,14 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q602" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q602" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
@@ -47243,10 +47251,14 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q603" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q603" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
@@ -47320,10 +47332,14 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q604" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q604" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
@@ -47397,10 +47413,14 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q605" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q605" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
@@ -47474,10 +47494,14 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q606" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q606" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
@@ -47551,10 +47575,14 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q607" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q607" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
@@ -47628,10 +47656,14 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q608" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q608" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
@@ -47705,10 +47737,14 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q609" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q609" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
@@ -47782,10 +47818,14 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q610" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q610" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
@@ -47859,10 +47899,14 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q611" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q611" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
@@ -47936,10 +47980,14 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q612" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q612" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
@@ -48013,10 +48061,14 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q613" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q613" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
@@ -48090,10 +48142,14 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q614" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q614" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
@@ -48167,10 +48223,14 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q615" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q615" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
@@ -48244,10 +48304,14 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q616" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q616" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
@@ -48321,10 +48385,14 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q617" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q617" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
@@ -48398,10 +48466,14 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q618" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q618" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
@@ -48475,10 +48547,14 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q619" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q619" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
@@ -48552,10 +48628,14 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q620" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q620" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
@@ -48629,10 +48709,14 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q621" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q621" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
@@ -48706,10 +48790,14 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q622" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q622" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
@@ -48783,10 +48871,14 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q623" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q623" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
@@ -48860,10 +48952,14 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q624" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q624" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
@@ -48937,10 +49033,14 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q625" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q625" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
@@ -49014,10 +49114,14 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q626" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q626" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
@@ -49091,10 +49195,14 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q627" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q627" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
@@ -49168,10 +49276,14 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q628" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q628" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
@@ -49245,10 +49357,14 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q629" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q629" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
@@ -49322,10 +49438,14 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q630" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q630" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
@@ -49399,10 +49519,14 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q631" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q631" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
@@ -49468,9 +49592,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N632" s="6" t="n">
-        <v>9.449999999999999</v>
-      </c>
+      <c r="N632" s="4" t="n"/>
       <c r="O632" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49478,10 +49600,14 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q632" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q632" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
@@ -49547,9 +49673,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N633" s="6" t="n">
-        <v>7.69</v>
-      </c>
+      <c r="N633" s="4" t="n"/>
       <c r="O633" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49557,10 +49681,14 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q633" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q633" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
@@ -49626,9 +49754,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N634" s="6" t="n">
-        <v>6.6</v>
-      </c>
+      <c r="N634" s="4" t="n"/>
       <c r="O634" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49636,10 +49762,14 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q634" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q634" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="4" t="inlineStr">
@@ -49705,9 +49835,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N635" s="6" t="n">
-        <v>8.56</v>
-      </c>
+      <c r="N635" s="4" t="n"/>
       <c r="O635" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49715,10 +49843,14 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q635" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q635" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
@@ -49784,9 +49916,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N636" s="6" t="n">
-        <v>10.24</v>
-      </c>
+      <c r="N636" s="4" t="n"/>
       <c r="O636" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49794,10 +49924,14 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q636" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q636" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="4" t="inlineStr">
@@ -49863,9 +49997,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N637" s="6" t="n">
-        <v>11.77</v>
-      </c>
+      <c r="N637" s="4" t="n"/>
       <c r="O637" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49873,10 +50005,14 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q637" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q637" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
@@ -49942,9 +50078,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N638" s="6" t="n">
-        <v>11.16</v>
-      </c>
+      <c r="N638" s="4" t="n"/>
       <c r="O638" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49952,10 +50086,14 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q638" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q638" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="4" t="inlineStr">
@@ -50021,9 +50159,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N639" s="6" t="n">
-        <v>11.15</v>
-      </c>
+      <c r="N639" s="4" t="n"/>
       <c r="O639" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50031,10 +50167,14 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q639" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q639" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
@@ -50100,9 +50240,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N640" s="6" t="n">
-        <v>14.53</v>
-      </c>
+      <c r="N640" s="4" t="n"/>
       <c r="O640" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50110,10 +50248,14 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q640" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q640" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="4" t="inlineStr">
@@ -50179,9 +50321,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N641" s="6" t="n">
-        <v>13.99</v>
-      </c>
+      <c r="N641" s="4" t="n"/>
       <c r="O641" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50189,10 +50329,14 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q641" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q641" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
@@ -50258,9 +50402,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N642" s="6" t="n">
-        <v>13.04</v>
-      </c>
+      <c r="N642" s="4" t="n"/>
       <c r="O642" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50268,10 +50410,14 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q642" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q642" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="4" t="inlineStr">
@@ -50337,9 +50483,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N643" s="6" t="n">
-        <v>16.17</v>
-      </c>
+      <c r="N643" s="4" t="n"/>
       <c r="O643" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50347,10 +50491,14 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q643" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q643" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
@@ -50416,9 +50564,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N644" s="6" t="n">
-        <v>16.78</v>
-      </c>
+      <c r="N644" s="4" t="n"/>
       <c r="O644" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50426,10 +50572,14 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q644" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q644" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="4" t="inlineStr">
@@ -50495,9 +50645,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N645" s="6" t="n">
-        <v>15.07</v>
-      </c>
+      <c r="N645" s="4" t="n"/>
       <c r="O645" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50505,10 +50653,14 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q645" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q645" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
@@ -50574,9 +50726,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N646" s="6" t="n">
-        <v>10.663</v>
-      </c>
+      <c r="N646" s="4" t="n"/>
       <c r="O646" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50584,10 +50734,14 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q646" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q646" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
@@ -50653,9 +50807,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N647" s="6" t="n">
-        <v>8.606</v>
-      </c>
+      <c r="N647" s="4" t="n"/>
       <c r="O647" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50663,10 +50815,14 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q647" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q647" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
@@ -50732,9 +50888,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N648" s="6" t="n">
-        <v>7.279</v>
-      </c>
+      <c r="N648" s="4" t="n"/>
       <c r="O648" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50742,10 +50896,14 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q648" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q648" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="4" t="inlineStr">
@@ -50811,9 +50969,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N649" s="6" t="n">
-        <v>6.245</v>
-      </c>
+      <c r="N649" s="4" t="n"/>
       <c r="O649" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50821,10 +50977,14 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q649" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q649" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
@@ -50890,9 +51050,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N650" s="6" t="n">
-        <v>6.097</v>
-      </c>
+      <c r="N650" s="4" t="n"/>
       <c r="O650" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50900,10 +51058,14 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q650" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q650" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
@@ -50969,9 +51131,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N651" s="6" t="n">
-        <v>7.112</v>
-      </c>
+      <c r="N651" s="4" t="n"/>
       <c r="O651" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50979,10 +51139,14 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q651" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q651" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
@@ -51048,9 +51212,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N652" s="6" t="n">
-        <v>6.902</v>
-      </c>
+      <c r="N652" s="4" t="n"/>
       <c r="O652" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51058,10 +51220,14 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q652" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q652" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="4" t="inlineStr">
@@ -51127,9 +51293,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N653" s="6" t="n">
-        <v>6.601</v>
-      </c>
+      <c r="N653" s="4" t="n"/>
       <c r="O653" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51137,10 +51301,14 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q653" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q653" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
@@ -51206,9 +51374,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N654" s="6" t="n">
-        <v>7.54</v>
-      </c>
+      <c r="N654" s="4" t="n"/>
       <c r="O654" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51216,10 +51382,14 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q654" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q654" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
@@ -51285,9 +51455,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N655" s="6" t="n">
-        <v>6.821</v>
-      </c>
+      <c r="N655" s="4" t="n"/>
       <c r="O655" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51295,10 +51463,14 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q655" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q655" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
@@ -51364,9 +51536,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N656" s="6" t="n">
-        <v>6.139</v>
-      </c>
+      <c r="N656" s="4" t="n"/>
       <c r="O656" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51374,10 +51544,14 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q656" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q656" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="4" t="inlineStr">
@@ -51443,9 +51617,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N657" s="6" t="n">
-        <v>5.319</v>
-      </c>
+      <c r="N657" s="4" t="n"/>
       <c r="O657" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51453,10 +51625,14 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q657" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q657" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
@@ -51522,9 +51698,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N658" s="6" t="n">
-        <v>5.045</v>
-      </c>
+      <c r="N658" s="4" t="n"/>
       <c r="O658" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51532,10 +51706,14 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q658" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q658" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="4" t="inlineStr">
@@ -51601,9 +51779,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N659" s="6" t="n">
-        <v>5.468</v>
-      </c>
+      <c r="N659" s="4" t="n"/>
       <c r="O659" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51611,10 +51787,14 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q659" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q659" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
@@ -51680,9 +51860,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N660" s="6" t="n">
-        <v>5.89</v>
-      </c>
+      <c r="N660" s="4" t="n"/>
       <c r="O660" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51690,10 +51868,14 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q660" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q660" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="4" t="inlineStr">
@@ -51759,9 +51941,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N661" s="6" t="n">
-        <v>7.53</v>
-      </c>
+      <c r="N661" s="4" t="n"/>
       <c r="O661" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51769,10 +51949,14 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q661" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q661" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="4" t="inlineStr">
@@ -51838,9 +52022,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N662" s="6" t="n">
-        <v>7.027</v>
-      </c>
+      <c r="N662" s="4" t="n"/>
       <c r="O662" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51848,10 +52030,14 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q662" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q662" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="4" t="inlineStr">
@@ -51917,9 +52103,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N663" s="6" t="n">
-        <v>5.646</v>
-      </c>
+      <c r="N663" s="4" t="n"/>
       <c r="O663" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51927,10 +52111,14 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q663" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q663" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="4" t="inlineStr">
@@ -51996,9 +52184,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N664" s="6" t="n">
-        <v>5.407</v>
-      </c>
+      <c r="N664" s="4" t="n"/>
       <c r="O664" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -52006,10 +52192,14 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q664" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q664" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="4" t="inlineStr">
@@ -52075,9 +52265,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N665" s="6" t="n">
-        <v>5.321</v>
-      </c>
+      <c r="N665" s="4" t="n"/>
       <c r="O665" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -52085,10 +52273,14 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q665" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q665" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="4" t="inlineStr">
@@ -52154,9 +52346,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N666" s="6" t="n">
-        <v>5.307</v>
-      </c>
+      <c r="N666" s="4" t="n"/>
       <c r="O666" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -52164,10 +52354,95 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="Q666" s="4" t="n"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q666" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B667" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C667" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D667" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E667" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F667" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G667" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H667" s="4" t="inlineStr">
+        <is>
+          <t>Mercado laboral</t>
+        </is>
+      </c>
+      <c r="I667" s="4" t="inlineStr">
+        <is>
+          <t>mercado_laboral</t>
+        </is>
+      </c>
+      <c r="J667" s="4" t="inlineStr">
+        <is>
+          <t>Desempleo</t>
+        </is>
+      </c>
+      <c r="K667" s="4" t="inlineStr">
+        <is>
+          <t>desempleo</t>
+        </is>
+      </c>
+      <c r="L667" s="4" t="inlineStr">
+        <is>
+          <t>SL.UEM.TOTL.ZS</t>
+        </is>
+      </c>
+      <c r="M667" s="4" t="inlineStr">
+        <is>
+          <t>Tasa de desempleo total</t>
+        </is>
+      </c>
+      <c r="N667" s="4" t="n"/>
+      <c r="O667" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P667" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Q667" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -52249,7 +52524,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -52270,7 +52545,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q667"/>
+  <dimension ref="A1:Q666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17095,7 +17095,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17557,7 +17557,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21323,7 +21323,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21785,7 +21785,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22324,7 +22324,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22786,7 +22786,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23793,7 +23793,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23872,7 +23872,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25215,7 +25215,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25294,7 +25294,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26400,7 +26400,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26554,7 +26554,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26708,7 +26708,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26862,7 +26862,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27016,7 +27016,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27247,7 +27247,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27555,7 +27555,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27940,7 +27940,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28017,7 +28017,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28171,7 +28171,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28248,7 +28248,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28325,7 +28325,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28633,7 +28633,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29342,7 +29342,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29500,7 +29500,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30211,7 +30211,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30448,7 +30448,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30922,7 +30922,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31159,7 +31159,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31317,7 +31317,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31396,7 +31396,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31475,7 +31475,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31785,7 +31785,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31939,7 +31939,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33325,7 +33325,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33633,7 +33633,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33787,7 +33787,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34338,7 +34338,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34812,7 +34812,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34891,7 +34891,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35128,7 +35128,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35286,7 +35286,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35444,7 +35444,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35602,7 +35602,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35681,7 +35681,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35839,7 +35839,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35918,7 +35918,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35997,7 +35997,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36076,7 +36076,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36234,7 +36234,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36392,7 +36392,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36629,7 +36629,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36785,7 +36785,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -36939,7 +36939,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37016,7 +37016,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37093,7 +37093,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37170,7 +37170,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37247,7 +37247,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37401,7 +37401,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37478,7 +37478,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37632,7 +37632,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37709,7 +37709,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37786,7 +37786,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37863,7 +37863,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38017,7 +38017,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38479,7 +38479,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38556,7 +38556,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38710,7 +38710,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38787,7 +38787,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -38941,7 +38941,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39018,7 +39018,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39095,7 +39095,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39253,7 +39253,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39332,7 +39332,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39490,7 +39490,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39727,7 +39727,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -39885,7 +39885,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -39964,7 +39964,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40043,7 +40043,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40359,7 +40359,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40438,7 +40438,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40833,7 +40833,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -40912,7 +40912,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -40991,7 +40991,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41070,7 +41070,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41228,7 +41228,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41307,7 +41307,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41465,7 +41465,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41544,7 +41544,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41623,7 +41623,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41702,7 +41702,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41781,7 +41781,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -41860,7 +41860,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -41937,7 +41937,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42014,7 +42014,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42091,7 +42091,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42168,7 +42168,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42245,7 +42245,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42476,7 +42476,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42553,7 +42553,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -42861,7 +42861,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -42938,7 +42938,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43015,7 +43015,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43169,7 +43169,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43246,7 +43246,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43477,7 +43477,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43631,7 +43631,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43708,7 +43708,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -43862,7 +43862,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -43939,7 +43939,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44170,7 +44170,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44405,7 +44405,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44563,7 +44563,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -44879,7 +44879,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -44958,7 +44958,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45037,7 +45037,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45274,7 +45274,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45432,7 +45432,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45511,7 +45511,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45590,7 +45590,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -45827,7 +45827,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -45906,7 +45906,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -45985,7 +45985,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46064,7 +46064,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46380,7 +46380,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46459,7 +46459,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46538,7 +46538,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46617,7 +46617,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -46854,7 +46854,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -46933,7 +46933,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47089,14 +47089,10 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q601" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q601" s="4" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
@@ -47170,14 +47166,10 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q602" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q602" s="4" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
@@ -47251,14 +47243,10 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q603" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q603" s="4" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
@@ -47332,14 +47320,10 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q604" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q604" s="4" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
@@ -47413,14 +47397,10 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q605" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q605" s="4" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
@@ -47494,14 +47474,10 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q606" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q606" s="4" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
@@ -47575,14 +47551,10 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q607" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q607" s="4" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
@@ -47656,14 +47628,10 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q608" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q608" s="4" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
@@ -47737,14 +47705,10 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q609" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q609" s="4" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
@@ -47818,14 +47782,10 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q610" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q610" s="4" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
@@ -47899,14 +47859,10 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q611" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q611" s="4" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
@@ -47980,14 +47936,10 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q612" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q612" s="4" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
@@ -48061,14 +48013,10 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q613" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q613" s="4" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
@@ -48142,14 +48090,10 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q614" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q614" s="4" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
@@ -48223,14 +48167,10 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q615" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q615" s="4" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
@@ -48304,14 +48244,10 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q616" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q616" s="4" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
@@ -48385,14 +48321,10 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q617" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q617" s="4" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
@@ -48466,14 +48398,10 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q618" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q618" s="4" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
@@ -48547,14 +48475,10 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q619" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q619" s="4" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
@@ -48628,14 +48552,10 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q620" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q620" s="4" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
@@ -48709,14 +48629,10 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q621" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q621" s="4" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
@@ -48790,14 +48706,10 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q622" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q622" s="4" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
@@ -48871,14 +48783,10 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q623" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q623" s="4" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
@@ -48952,14 +48860,10 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q624" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q624" s="4" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
@@ -49033,14 +48937,10 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q625" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q625" s="4" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
@@ -49114,14 +49014,10 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q626" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q626" s="4" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
@@ -49195,14 +49091,10 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q627" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q627" s="4" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
@@ -49276,14 +49168,10 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q628" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q628" s="4" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
@@ -49357,14 +49245,10 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q629" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q629" s="4" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
@@ -49438,14 +49322,10 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q630" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q630" s="4" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
@@ -49519,14 +49399,10 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q631" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q631" s="4" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
@@ -49592,7 +49468,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N632" s="4" t="n"/>
+      <c r="N632" s="6" t="n">
+        <v>9.449999999999999</v>
+      </c>
       <c r="O632" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49600,14 +49478,10 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q632" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q632" s="4" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
@@ -49673,7 +49547,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N633" s="4" t="n"/>
+      <c r="N633" s="6" t="n">
+        <v>7.69</v>
+      </c>
       <c r="O633" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49681,14 +49557,10 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q633" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q633" s="4" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
@@ -49754,7 +49626,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N634" s="4" t="n"/>
+      <c r="N634" s="6" t="n">
+        <v>6.6</v>
+      </c>
       <c r="O634" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49762,14 +49636,10 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q634" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q634" s="4" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="4" t="inlineStr">
@@ -49835,7 +49705,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N635" s="4" t="n"/>
+      <c r="N635" s="6" t="n">
+        <v>8.56</v>
+      </c>
       <c r="O635" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49843,14 +49715,10 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q635" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q635" s="4" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
@@ -49916,7 +49784,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N636" s="4" t="n"/>
+      <c r="N636" s="6" t="n">
+        <v>10.24</v>
+      </c>
       <c r="O636" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -49924,14 +49794,10 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q636" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q636" s="4" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="4" t="inlineStr">
@@ -49997,7 +49863,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N637" s="4" t="n"/>
+      <c r="N637" s="6" t="n">
+        <v>11.77</v>
+      </c>
       <c r="O637" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50005,14 +49873,10 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q637" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q637" s="4" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
@@ -50078,7 +49942,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N638" s="4" t="n"/>
+      <c r="N638" s="6" t="n">
+        <v>11.16</v>
+      </c>
       <c r="O638" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50086,14 +49952,10 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q638" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q638" s="4" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="4" t="inlineStr">
@@ -50159,7 +50021,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N639" s="4" t="n"/>
+      <c r="N639" s="6" t="n">
+        <v>11.15</v>
+      </c>
       <c r="O639" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50167,14 +50031,10 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q639" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q639" s="4" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
@@ -50240,7 +50100,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N640" s="4" t="n"/>
+      <c r="N640" s="6" t="n">
+        <v>14.53</v>
+      </c>
       <c r="O640" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50248,14 +50110,10 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q640" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q640" s="4" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="4" t="inlineStr">
@@ -50321,7 +50179,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N641" s="4" t="n"/>
+      <c r="N641" s="6" t="n">
+        <v>13.99</v>
+      </c>
       <c r="O641" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50329,14 +50189,10 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q641" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q641" s="4" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
@@ -50402,7 +50258,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N642" s="4" t="n"/>
+      <c r="N642" s="6" t="n">
+        <v>13.04</v>
+      </c>
       <c r="O642" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50410,14 +50268,10 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q642" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q642" s="4" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="4" t="inlineStr">
@@ -50483,7 +50337,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N643" s="4" t="n"/>
+      <c r="N643" s="6" t="n">
+        <v>16.17</v>
+      </c>
       <c r="O643" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50491,14 +50347,10 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q643" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q643" s="4" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
@@ -50564,7 +50416,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N644" s="4" t="n"/>
+      <c r="N644" s="6" t="n">
+        <v>16.78</v>
+      </c>
       <c r="O644" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50572,14 +50426,10 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q644" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q644" s="4" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="4" t="inlineStr">
@@ -50645,7 +50495,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N645" s="4" t="n"/>
+      <c r="N645" s="6" t="n">
+        <v>15.07</v>
+      </c>
       <c r="O645" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50653,14 +50505,10 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q645" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q645" s="4" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
@@ -50726,7 +50574,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N646" s="4" t="n"/>
+      <c r="N646" s="6" t="n">
+        <v>10.663</v>
+      </c>
       <c r="O646" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50734,14 +50584,10 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q646" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q646" s="4" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
@@ -50807,7 +50653,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N647" s="4" t="n"/>
+      <c r="N647" s="6" t="n">
+        <v>8.606</v>
+      </c>
       <c r="O647" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50815,14 +50663,10 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q647" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q647" s="4" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
@@ -50888,7 +50732,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N648" s="4" t="n"/>
+      <c r="N648" s="6" t="n">
+        <v>7.279</v>
+      </c>
       <c r="O648" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50896,14 +50742,10 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q648" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q648" s="4" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="4" t="inlineStr">
@@ -50969,7 +50811,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N649" s="4" t="n"/>
+      <c r="N649" s="6" t="n">
+        <v>6.245</v>
+      </c>
       <c r="O649" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -50977,14 +50821,10 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q649" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q649" s="4" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
@@ -51050,7 +50890,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N650" s="4" t="n"/>
+      <c r="N650" s="6" t="n">
+        <v>6.097</v>
+      </c>
       <c r="O650" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51058,14 +50900,10 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q650" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q650" s="4" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
@@ -51131,7 +50969,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N651" s="4" t="n"/>
+      <c r="N651" s="6" t="n">
+        <v>7.112</v>
+      </c>
       <c r="O651" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51139,14 +50979,10 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q651" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q651" s="4" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
@@ -51212,7 +51048,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N652" s="4" t="n"/>
+      <c r="N652" s="6" t="n">
+        <v>6.902</v>
+      </c>
       <c r="O652" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51220,14 +51058,10 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q652" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q652" s="4" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="4" t="inlineStr">
@@ -51293,7 +51127,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N653" s="4" t="n"/>
+      <c r="N653" s="6" t="n">
+        <v>6.601</v>
+      </c>
       <c r="O653" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51301,14 +51137,10 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q653" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q653" s="4" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
@@ -51374,7 +51206,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N654" s="4" t="n"/>
+      <c r="N654" s="6" t="n">
+        <v>7.54</v>
+      </c>
       <c r="O654" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51382,14 +51216,10 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q654" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q654" s="4" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
@@ -51455,7 +51285,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N655" s="4" t="n"/>
+      <c r="N655" s="6" t="n">
+        <v>6.821</v>
+      </c>
       <c r="O655" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51463,14 +51295,10 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q655" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q655" s="4" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
@@ -51536,7 +51364,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N656" s="4" t="n"/>
+      <c r="N656" s="6" t="n">
+        <v>6.139</v>
+      </c>
       <c r="O656" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51544,14 +51374,10 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q656" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q656" s="4" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="4" t="inlineStr">
@@ -51617,7 +51443,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N657" s="4" t="n"/>
+      <c r="N657" s="6" t="n">
+        <v>5.319</v>
+      </c>
       <c r="O657" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51625,14 +51453,10 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q657" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q657" s="4" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
@@ -51698,7 +51522,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N658" s="4" t="n"/>
+      <c r="N658" s="6" t="n">
+        <v>5.045</v>
+      </c>
       <c r="O658" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51706,14 +51532,10 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q658" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q658" s="4" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="4" t="inlineStr">
@@ -51779,7 +51601,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N659" s="4" t="n"/>
+      <c r="N659" s="6" t="n">
+        <v>5.468</v>
+      </c>
       <c r="O659" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51787,14 +51611,10 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q659" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q659" s="4" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
@@ -51860,7 +51680,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N660" s="4" t="n"/>
+      <c r="N660" s="6" t="n">
+        <v>5.89</v>
+      </c>
       <c r="O660" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51868,14 +51690,10 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q660" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q660" s="4" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="4" t="inlineStr">
@@ -51941,7 +51759,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N661" s="4" t="n"/>
+      <c r="N661" s="6" t="n">
+        <v>7.53</v>
+      </c>
       <c r="O661" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -51949,14 +51769,10 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q661" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q661" s="4" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="4" t="inlineStr">
@@ -52022,7 +51838,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N662" s="4" t="n"/>
+      <c r="N662" s="6" t="n">
+        <v>7.027</v>
+      </c>
       <c r="O662" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -52030,14 +51848,10 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q662" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q662" s="4" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="4" t="inlineStr">
@@ -52103,7 +51917,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N663" s="4" t="n"/>
+      <c r="N663" s="6" t="n">
+        <v>5.646</v>
+      </c>
       <c r="O663" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -52111,14 +51927,10 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q663" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q663" s="4" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="4" t="inlineStr">
@@ -52184,7 +51996,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N664" s="4" t="n"/>
+      <c r="N664" s="6" t="n">
+        <v>5.407</v>
+      </c>
       <c r="O664" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -52192,14 +52006,10 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q664" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q664" s="4" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="4" t="inlineStr">
@@ -52265,7 +52075,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N665" s="4" t="n"/>
+      <c r="N665" s="6" t="n">
+        <v>5.321</v>
+      </c>
       <c r="O665" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -52273,14 +52085,10 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q665" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q665" s="4" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="4" t="inlineStr">
@@ -52346,7 +52154,9 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N666" s="4" t="n"/>
+      <c r="N666" s="6" t="n">
+        <v>5.307</v>
+      </c>
       <c r="O666" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -52354,95 +52164,10 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q666" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B667" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C667" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D667" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E667" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F667" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G667" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H667" s="4" t="inlineStr">
-        <is>
-          <t>Mercado laboral</t>
-        </is>
-      </c>
-      <c r="I667" s="4" t="inlineStr">
-        <is>
-          <t>mercado_laboral</t>
-        </is>
-      </c>
-      <c r="J667" s="4" t="inlineStr">
-        <is>
-          <t>Desempleo</t>
-        </is>
-      </c>
-      <c r="K667" s="4" t="inlineStr">
-        <is>
-          <t>desempleo</t>
-        </is>
-      </c>
-      <c r="L667" s="4" t="inlineStr">
-        <is>
-          <t>SL.UEM.TOTL.ZS</t>
-        </is>
-      </c>
-      <c r="M667" s="4" t="inlineStr">
-        <is>
-          <t>Tasa de desempleo total</t>
-        </is>
-      </c>
-      <c r="N667" s="4" t="n"/>
-      <c r="O667" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P667" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q667" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q666" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -52524,7 +52249,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -52545,7 +52270,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17095,7 +17095,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17557,7 +17557,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21323,7 +21323,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21785,7 +21785,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22324,7 +22324,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22786,7 +22786,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23793,7 +23793,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23872,7 +23872,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25215,7 +25215,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25294,7 +25294,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26400,7 +26400,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26554,7 +26554,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26708,7 +26708,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26862,7 +26862,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27016,7 +27016,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27247,7 +27247,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27555,7 +27555,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27940,7 +27940,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28017,7 +28017,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28171,7 +28171,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28248,7 +28248,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28325,7 +28325,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28633,7 +28633,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29342,7 +29342,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29500,7 +29500,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30211,7 +30211,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30448,7 +30448,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30922,7 +30922,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31159,7 +31159,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31317,7 +31317,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31396,7 +31396,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31475,7 +31475,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31785,7 +31785,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31939,7 +31939,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33325,7 +33325,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33633,7 +33633,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33787,7 +33787,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34338,7 +34338,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34812,7 +34812,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34891,7 +34891,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35128,7 +35128,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35286,7 +35286,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35444,7 +35444,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35602,7 +35602,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35681,7 +35681,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35839,7 +35839,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35918,7 +35918,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35997,7 +35997,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36076,7 +36076,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36234,7 +36234,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36392,7 +36392,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36629,7 +36629,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36785,7 +36785,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -36939,7 +36939,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37016,7 +37016,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37093,7 +37093,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37170,7 +37170,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37247,7 +37247,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37401,7 +37401,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37478,7 +37478,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37632,7 +37632,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37709,7 +37709,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37786,7 +37786,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37863,7 +37863,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38017,7 +38017,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38479,7 +38479,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38556,7 +38556,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38710,7 +38710,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38787,7 +38787,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -38941,7 +38941,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39018,7 +39018,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39095,7 +39095,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39253,7 +39253,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39332,7 +39332,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39490,7 +39490,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39727,7 +39727,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -39885,7 +39885,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -39964,7 +39964,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40043,7 +40043,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40359,7 +40359,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40438,7 +40438,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40833,7 +40833,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -40912,7 +40912,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -40991,7 +40991,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41070,7 +41070,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41228,7 +41228,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41307,7 +41307,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41465,7 +41465,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41544,7 +41544,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41623,7 +41623,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41702,7 +41702,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41781,7 +41781,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -41860,7 +41860,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -41937,7 +41937,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42014,7 +42014,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42091,7 +42091,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42168,7 +42168,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42245,7 +42245,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42476,7 +42476,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42553,7 +42553,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -42861,7 +42861,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -42938,7 +42938,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43015,7 +43015,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43169,7 +43169,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43246,7 +43246,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43477,7 +43477,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43631,7 +43631,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43708,7 +43708,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -43862,7 +43862,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -43939,7 +43939,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44170,7 +44170,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44405,7 +44405,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44563,7 +44563,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -44879,7 +44879,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -44958,7 +44958,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45037,7 +45037,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45274,7 +45274,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45432,7 +45432,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45511,7 +45511,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45590,7 +45590,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -45827,7 +45827,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -45906,7 +45906,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -45985,7 +45985,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46064,7 +46064,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46380,7 +46380,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46459,7 +46459,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46538,7 +46538,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46617,7 +46617,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -46854,7 +46854,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -46933,7 +46933,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47089,7 +47089,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47166,7 +47166,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47320,7 +47320,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47474,7 +47474,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47551,7 +47551,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -47628,7 +47628,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -47705,7 +47705,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -47782,7 +47782,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -47859,7 +47859,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -47936,7 +47936,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48013,7 +48013,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48090,7 +48090,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48167,7 +48167,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48321,7 +48321,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48398,7 +48398,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48475,7 +48475,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -48629,7 +48629,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -48706,7 +48706,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -48783,7 +48783,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -48860,7 +48860,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -48937,7 +48937,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49014,7 +49014,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49091,7 +49091,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49168,7 +49168,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49322,7 +49322,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49399,7 +49399,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49478,7 +49478,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -49557,7 +49557,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -49636,7 +49636,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -49715,7 +49715,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -49794,7 +49794,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -49873,7 +49873,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -49952,7 +49952,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50031,7 +50031,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50110,7 +50110,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50189,7 +50189,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50268,7 +50268,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50347,7 +50347,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50426,7 +50426,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50505,7 +50505,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -50663,7 +50663,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -50742,7 +50742,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -50821,7 +50821,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -50900,7 +50900,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -50979,7 +50979,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51058,7 +51058,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51137,7 +51137,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51216,7 +51216,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51295,7 +51295,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -51532,7 +51532,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -51690,7 +51690,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -51769,7 +51769,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -51848,7 +51848,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -51927,7 +51927,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52006,7 +52006,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52085,7 +52085,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52164,7 +52164,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52249,7 +52249,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17095,7 +17095,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17557,7 +17557,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21323,7 +21323,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21785,7 +21785,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22324,7 +22324,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22786,7 +22786,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23793,7 +23793,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23872,7 +23872,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25215,7 +25215,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25294,7 +25294,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26400,7 +26400,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26554,7 +26554,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26708,7 +26708,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26862,7 +26862,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27016,7 +27016,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27247,7 +27247,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27555,7 +27555,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27940,7 +27940,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28017,7 +28017,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28171,7 +28171,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28248,7 +28248,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28325,7 +28325,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28633,7 +28633,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29342,7 +29342,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29500,7 +29500,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30211,7 +30211,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30448,7 +30448,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30922,7 +30922,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31159,7 +31159,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31317,7 +31317,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31396,7 +31396,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31475,7 +31475,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31785,7 +31785,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31939,7 +31939,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33325,7 +33325,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33633,7 +33633,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33787,7 +33787,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34338,7 +34338,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34812,7 +34812,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34891,7 +34891,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35128,7 +35128,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35286,7 +35286,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35444,7 +35444,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35602,7 +35602,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35681,7 +35681,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35839,7 +35839,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35918,7 +35918,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35997,7 +35997,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36076,7 +36076,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36234,7 +36234,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36392,7 +36392,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36629,7 +36629,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36785,7 +36785,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -36939,7 +36939,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37016,7 +37016,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37093,7 +37093,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37170,7 +37170,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37247,7 +37247,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37401,7 +37401,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37478,7 +37478,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37632,7 +37632,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37709,7 +37709,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37786,7 +37786,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37863,7 +37863,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38017,7 +38017,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38479,7 +38479,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38556,7 +38556,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38710,7 +38710,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38787,7 +38787,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -38941,7 +38941,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39018,7 +39018,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39095,7 +39095,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39253,7 +39253,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39332,7 +39332,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39490,7 +39490,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39727,7 +39727,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -39885,7 +39885,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -39964,7 +39964,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40043,7 +40043,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40359,7 +40359,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40438,7 +40438,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40833,7 +40833,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -40912,7 +40912,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -40991,7 +40991,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41070,7 +41070,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41228,7 +41228,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41307,7 +41307,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41465,7 +41465,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41544,7 +41544,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41623,7 +41623,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41702,7 +41702,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41781,7 +41781,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -41860,7 +41860,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -41937,7 +41937,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42014,7 +42014,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42091,7 +42091,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42168,7 +42168,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42245,7 +42245,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42476,7 +42476,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42553,7 +42553,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -42861,7 +42861,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -42938,7 +42938,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43015,7 +43015,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43169,7 +43169,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43246,7 +43246,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43477,7 +43477,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43631,7 +43631,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43708,7 +43708,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -43862,7 +43862,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -43939,7 +43939,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44170,7 +44170,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44405,7 +44405,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44563,7 +44563,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -44879,7 +44879,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -44958,7 +44958,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45037,7 +45037,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45274,7 +45274,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45432,7 +45432,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45511,7 +45511,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45590,7 +45590,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -45827,7 +45827,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -45906,7 +45906,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -45985,7 +45985,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46064,7 +46064,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46380,7 +46380,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46459,7 +46459,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46538,7 +46538,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46617,7 +46617,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -46854,7 +46854,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -46933,7 +46933,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47089,7 +47089,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47166,7 +47166,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47320,7 +47320,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47474,7 +47474,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47551,7 +47551,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -47628,7 +47628,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -47705,7 +47705,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -47782,7 +47782,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -47859,7 +47859,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -47936,7 +47936,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48013,7 +48013,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48090,7 +48090,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48167,7 +48167,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48321,7 +48321,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48398,7 +48398,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48475,7 +48475,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -48629,7 +48629,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -48706,7 +48706,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -48783,7 +48783,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -48860,7 +48860,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -48937,7 +48937,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49014,7 +49014,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49091,7 +49091,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49168,7 +49168,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49322,7 +49322,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49399,7 +49399,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49478,7 +49478,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -49557,7 +49557,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -49636,7 +49636,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -49715,7 +49715,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -49794,7 +49794,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -49873,7 +49873,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -49952,7 +49952,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50031,7 +50031,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50110,7 +50110,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50189,7 +50189,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50268,7 +50268,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50347,7 +50347,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50426,7 +50426,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50505,7 +50505,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -50663,7 +50663,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -50742,7 +50742,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -50821,7 +50821,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -50900,7 +50900,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -50979,7 +50979,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51058,7 +51058,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51137,7 +51137,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51216,7 +51216,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51295,7 +51295,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -51532,7 +51532,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -51690,7 +51690,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -51769,7 +51769,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -51848,7 +51848,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -51927,7 +51927,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52006,7 +52006,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52085,7 +52085,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52164,7 +52164,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52249,7 +52249,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
